--- a/education_forms/030_reading_assessment_form--education_forms.xlsx
+++ b/education_forms/030_reading_assessment_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'every_day'}</t>
+          <t>every_day</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Every day'}</t>
+          <t>Every day</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'every_week'}</t>
+          <t>every_week</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Every week'}</t>
+          <t>Every week</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'fiction'}</t>
+          <t>fiction</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Fiction'}</t>
+          <t>Fiction</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'non-fiction'}</t>
+          <t>non-fiction</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Non-Fiction'}</t>
+          <t>Non-Fiction</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'comic'}</t>
+          <t>comic</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Comic'}</t>
+          <t>Comic</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'graphic_novel'}</t>
+          <t>graphic_novel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Graphic Novel'}</t>
+          <t>Graphic Novel</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'print'}</t>
+          <t>print</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Print'}</t>
+          <t>Print</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'digital'}</t>
+          <t>digital</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Digital'}</t>
+          <t>Digital</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'audio'}</t>
+          <t>audio</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Audio'}</t>
+          <t>Audio</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'fast'}</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Fast'}</t>
+          <t>Fast</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'slow'}</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Slow'}</t>
+          <t>Slow</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
